--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486292_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486292_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9677</v>
+        <v>8.326000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2495</v>
+        <v>7.3612</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.9648</v>
       </c>
       <c r="G2" t="n">
         <v>6.8262</v>
@@ -610,13 +610,13 @@
         <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7487</v>
+        <v>-1.3904</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1322</v>
+        <v>-0.8857</v>
       </c>
       <c r="V2" t="n">
         <v>2.4552</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5628</v>
+        <v>2.1313</v>
       </c>
       <c r="E3" t="n">
         <v>0.0269</v>
       </c>
       <c r="F3" t="n">
-        <v>2.536</v>
+        <v>2.1045</v>
       </c>
       <c r="G3" t="n">
         <v>2.9194</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0738</v>
+        <v>-0.5053</v>
       </c>
       <c r="T3" t="n">
         <v>-0.7534999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6797</v>
+        <v>0.2481</v>
       </c>
       <c r="V3" t="n">
         <v>0.3698</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>M. TOWNES VILLAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.354</v>
+        <v>1.6688</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8675</v>
+        <v>2.8855</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5134</v>
+        <v>-1.2167</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8349</v>
+        <v>6.0317</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0461</v>
+        <v>4.0786</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2112</v>
+        <v>1.9531</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6877</v>
+        <v>6.2933</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4964</v>
+        <v>3.7689</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1912</v>
+        <v>2.5245</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8528</v>
+        <v>-0.2616</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4504</v>
+        <v>0.3098</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4024</v>
+        <v>-0.5714</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.435</v>
+        <v>-0.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7589</v>
+        <v>-1.4075</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0297</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2708</v>
+        <v>-0.6973</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1952</v>
+        <v>-2.0854</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>-2.6504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TOWNES VILLAR</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4029</v>
+        <v>0.9499</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7737</v>
+        <v>0.4409</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3708</v>
+        <v>0.509</v>
       </c>
       <c r="G5" t="n">
-        <v>6.0317</v>
+        <v>1.1961</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0786</v>
+        <v>0.1793</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9531</v>
+        <v>1.0168</v>
       </c>
       <c r="J5" t="n">
-        <v>6.2933</v>
+        <v>1.6975</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7689</v>
+        <v>0.8942</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5245</v>
+        <v>0.8032</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2616</v>
+        <v>-0.5013</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3098</v>
+        <v>-0.7149</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5714</v>
+        <v>0.2136</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6734</v>
+        <v>-0.2244</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.822</v>
+        <v>-0.3425</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8514</v>
+        <v>0.1181</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.0854</v>
+        <v>-1.1093</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.9141</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.6504</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2273</v>
+        <v>0.9205</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4409</v>
+        <v>1.5264</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7864</v>
+        <v>-0.6059</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1961</v>
+        <v>0.8349</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1793</v>
+        <v>1.0461</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0168</v>
+        <v>-0.2112</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6975</v>
+        <v>1.6877</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8942</v>
+        <v>1.4964</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8032</v>
+        <v>0.1912</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5013</v>
+        <v>-0.8528</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7149</v>
+        <v>-0.4504</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2136</v>
+        <v>-0.4024</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>0.053</v>
+        <v>0.3254</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3425</v>
+        <v>0.6886</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3955</v>
+        <v>-0.3632</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1093</v>
+        <v>0.1952</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.9141</v>
+        <v>1.3252</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6049</v>
+        <v>-0.3879</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2419</v>
+        <v>-0.2834</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.363</v>
+        <v>-0.1044</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7639</v>
+        <v>1.5378</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8181</v>
+        <v>-2.3054</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0542</v>
+        <v>3.8432</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2827</v>
+        <v>2.7604</v>
       </c>
       <c r="K7" t="n">
-        <v>1.168</v>
+        <v>-1.5052</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1147</v>
+        <v>4.2656</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5188</v>
+        <v>-1.2226</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3499</v>
+        <v>-0.8003</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1689</v>
+        <v>-0.4224</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8032</v>
+        <v>-1.1638</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4795</v>
+        <v>-0.3245</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3237</v>
+        <v>-0.8394</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7395</v>
+        <v>-0.5443</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>-0.5443</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7963</v>
+        <v>-0.4199</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5069</v>
+        <v>-0.2419</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2894</v>
+        <v>-0.1781</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5378</v>
+        <v>0.7639</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.3054</v>
+        <v>0.8181</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8432</v>
+        <v>-0.0542</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7604</v>
+        <v>1.2827</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5052</v>
+        <v>1.168</v>
       </c>
       <c r="L8" t="n">
-        <v>4.2656</v>
+        <v>0.1147</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2226</v>
+        <v>-0.5188</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8003</v>
+        <v>-0.3499</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4224</v>
+        <v>-0.1689</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5723</v>
+        <v>-0.6183</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.548</v>
+        <v>-0.4795</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0243</v>
+        <v>-0.1388</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5443</v>
+        <v>0.7395</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.5443</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.975</v>
+        <v>-0.6758</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3995</v>
+        <v>-0.448</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4245</v>
+        <v>-0.2278</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.08459999999999999</v>
+        <v>0.0612</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1561</v>
+        <v>-2.2904</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2408</v>
+        <v>2.3515</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4415</v>
+        <v>2.2137</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4089</v>
+        <v>-0.9426</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9674</v>
+        <v>3.1564</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5261</v>
+        <v>-2.1526</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2528</v>
+        <v>-1.3477</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2733</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0875</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
         <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8479</v>
+        <v>-0.7369</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4867</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0945</v>
+        <v>-0.2503</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1652</v>
+        <v>-0.8247</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7833</v>
+        <v>-1.0642</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3819</v>
+        <v>0.2396</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0612</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2904</v>
+        <v>2.1561</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3515</v>
+        <v>-2.2408</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2137</v>
+        <v>0.4415</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9426</v>
+        <v>2.4089</v>
       </c>
       <c r="L10" t="n">
-        <v>3.1564</v>
+        <v>-1.9674</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1526</v>
+        <v>-0.5261</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3477</v>
+        <v>-0.2528</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.2733</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
         <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2263</v>
+        <v>-0.6976</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.822</v>
+        <v>-0.4182</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4044</v>
+        <v>-0.2794</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7202</v>
+        <v>-2.435</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9845</v>
+        <v>-4.761</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2643</v>
+        <v>2.326</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9184</v>
@@ -1312,13 +1312,13 @@
         <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6919</v>
+        <v>-0.4068</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.822</v>
+        <v>-0.5984</v>
       </c>
       <c r="U11" t="n">
-        <v>0.13</v>
+        <v>0.1917</v>
       </c>
       <c r="V11" t="n">
         <v>0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.2531</v>
+        <v>9.2532</v>
       </c>
       <c r="E12" t="n">
-        <v>5.4424</v>
+        <v>5.442400000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8109</v>
+        <v>3.811</v>
       </c>
       <c r="G12" t="n">
         <v>19.1682</v>
@@ -1366,13 +1366,13 @@
         <v>25.0626</v>
       </c>
       <c r="K12" t="n">
-        <v>9.141299999999999</v>
+        <v>9.141300000000001</v>
       </c>
       <c r="L12" t="n">
         <v>15.9213</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.894499999999999</v>
+        <v>-5.894500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-3.6831</v>
@@ -1390,22 +1390,22 @@
         <v>18.4882</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.8256</v>
+        <v>-6.825599999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.9298</v>
+        <v>-3.929600000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.8961</v>
+        <v>-2.8962</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9140999999999995</v>
+        <v>-0.9140999999999997</v>
       </c>
       <c r="W12" t="n">
         <v>4.972399999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.8864</v>
+        <v>-5.886399999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4878</v>
+        <v>4.6304</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2876</v>
+        <v>3.3994</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2002</v>
+        <v>1.231</v>
       </c>
       <c r="G13" t="n">
         <v>3.2872</v>
@@ -1468,13 +1468,13 @@
         <v>1.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.9082</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4026</v>
+        <v>0.5143</v>
       </c>
       <c r="U13" t="n">
-        <v>0.363</v>
+        <v>0.3939</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ALONSO RUIZ</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3751</v>
+        <v>1.8246</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4541</v>
+        <v>2.4989</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0791</v>
+        <v>-0.6743</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.4007</v>
+        <v>0.3607</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.368</v>
+        <v>1.3352</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0327</v>
+        <v>-0.9745</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4131</v>
+        <v>3.4064</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0434</v>
+        <v>2.4486</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6303</v>
+        <v>0.9578</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8138</v>
+        <v>-3.0458</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4114</v>
+        <v>-1.1134</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4024</v>
+        <v>-1.9324</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5225</v>
+        <v>-0.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>0.144</v>
+        <v>0.2899</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1286</v>
+        <v>-0.0577</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0154</v>
+        <v>0.3476</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1093</v>
+        <v>2.044</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.0207</v>
+        <v>0.7188</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>A. ALONSO RUIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1733</v>
+        <v>1.5099</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9401</v>
+        <v>1.3424</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7668</v>
+        <v>0.1675</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3607</v>
+        <v>-1.4007</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3352</v>
+        <v>-0.368</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9745</v>
+        <v>-1.0327</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4064</v>
+        <v>0.4131</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4486</v>
+        <v>1.0434</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9578</v>
+        <v>-0.6303</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.0458</v>
+        <v>-1.8138</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1134</v>
+        <v>-1.4114</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.9324</v>
+        <v>-0.4024</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3613</v>
+        <v>0.2788</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6165</v>
+        <v>0.0168</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2551</v>
+        <v>0.262</v>
       </c>
       <c r="V15" t="n">
-        <v>2.044</v>
+        <v>1.1093</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7188</v>
+        <v>-0.0207</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>M. JACKSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2378</v>
+        <v>1.0348</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1148</v>
+        <v>2.2533</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3526</v>
+        <v>-1.2184</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.4767</v>
+        <v>0.3455</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4623</v>
+        <v>0.0092</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0144</v>
+        <v>0.3363</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3236</v>
+        <v>2.9617</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1706</v>
+        <v>0.6086</v>
       </c>
       <c r="L16" t="n">
-        <v>0.153</v>
+        <v>2.3531</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8003</v>
+        <v>-2.6162</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6328</v>
+        <v>-0.5994</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1674</v>
+        <v>-2.0169</v>
       </c>
       <c r="P16" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>3.0451</v>
+        <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2349</v>
+        <v>0.3191</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7367</v>
+        <v>0.1839</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4982</v>
+        <v>0.1352</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3904</v>
+        <v>-0.9347</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. JACKSON</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0906</v>
+        <v>-0.109</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2474</v>
+        <v>-1.3384</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1568</v>
+        <v>1.2293</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3455</v>
+        <v>-1.4767</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0092</v>
+        <v>-0.4623</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3363</v>
+        <v>-1.0144</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9617</v>
+        <v>0.3236</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6086</v>
+        <v>0.1706</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3531</v>
+        <v>0.153</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6162</v>
+        <v>-1.8003</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5994</v>
+        <v>-0.6328</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0169</v>
+        <v>-1.1674</v>
       </c>
       <c r="P17" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3926</v>
+        <v>3.0451</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6251</v>
+        <v>0.8881</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.822</v>
+        <v>0.5131</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1968</v>
+        <v>0.3749</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9347</v>
+        <v>-0.3904</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ZIDEK</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5792</v>
+        <v>-1.2182</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3898</v>
+        <v>-1.3956</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.969</v>
+        <v>0.1774</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.1449</v>
+        <v>-2.1987</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4834</v>
+        <v>-2.0681</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6615</v>
+        <v>-0.1307</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0506</v>
+        <v>-1.4154</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8276</v>
+        <v>-1.4536</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8781</v>
+        <v>0.0382</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0943</v>
+        <v>-0.7834</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3109</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7834</v>
+        <v>-0.1689</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>2.153</v>
+        <v>0.3503</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5502</v>
+        <v>0.0421</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6028</v>
+        <v>0.3082</v>
       </c>
       <c r="V18" t="n">
         <v>0.1952</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0209</v>
+        <v>-1.3049</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.016</v>
+        <v>1.101</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0049</v>
+        <v>-2.4059</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.6847</v>
+        <v>-1.0143</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0278</v>
+        <v>1.1619</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.6568</v>
+        <v>-2.1762</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.3999</v>
+        <v>1.5325</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.611</v>
+        <v>1.6274</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.789</v>
+        <v>-0.0948</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2847</v>
+        <v>-2.5468</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4169</v>
+        <v>-0.4654</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8679</v>
+        <v>-2.0814</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6101</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8276</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4235</v>
+        <v>0.7964</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2762</v>
+        <v>0.2656</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1472</v>
+        <v>0.5308</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3698</v>
+        <v>-1.3045</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3252</v>
+        <v>0.3904</v>
       </c>
       <c r="X19" t="n">
         <v>-1.695</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>J. ZIDEK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1796</v>
+        <v>-1.7083</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1721</v>
+        <v>-0.616</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0076</v>
+        <v>-1.0923</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1987</v>
+        <v>-3.1449</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0681</v>
+        <v>-0.4834</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1307</v>
+        <v>-2.6615</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4154</v>
+        <v>-0.0506</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4536</v>
+        <v>0.8276</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0382</v>
+        <v>-0.8781</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7834</v>
+        <v>-3.0943</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-1.3109</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1689</v>
+        <v>-1.7834</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3889</v>
+        <v>1.0239</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2656</v>
+        <v>0.5444</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1233</v>
+        <v>0.4795</v>
       </c>
       <c r="V20" t="n">
         <v>0.1952</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2124</v>
+        <v>-1.9804</v>
       </c>
       <c r="E21" t="n">
-        <v>1.101</v>
+        <v>-1.5748</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3134</v>
+        <v>-0.4056</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0143</v>
+        <v>-5.6847</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1619</v>
+        <v>-1.0278</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1762</v>
+        <v>-4.6568</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5325</v>
+        <v>-3.3999</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6274</v>
+        <v>-0.611</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0948</v>
+        <v>-2.789</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5468</v>
+        <v>-2.2847</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4654</v>
+        <v>-0.4169</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0814</v>
+        <v>-1.8679</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>2.6101</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>2.8276</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8889</v>
+        <v>1.464</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2656</v>
+        <v>0.7174</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6233</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3045</v>
+        <v>-0.3698</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3904</v>
+        <v>1.3252</v>
       </c>
       <c r="X21" t="n">
         <v>-1.695</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6765</v>
+        <v>-4.8462</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0593</v>
+        <v>-3.5063</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6173</v>
+        <v>-1.3398</v>
       </c>
       <c r="G22" t="n">
         <v>-3.5601</v>
@@ -2170,13 +2170,13 @@
         <v>1.9576</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4061</v>
+        <v>0.2364</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6682</v>
+        <v>0.2211</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2621</v>
+        <v>0.0153</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.9493</v>
+        <v>-7.086</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.8688</v>
+        <v>-5.9747</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0805</v>
+        <v>-1.1113</v>
       </c>
       <c r="G23" t="n">
         <v>-4.6814</v>
@@ -2248,13 +2248,13 @@
         <v>2.3926</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5926</v>
+        <v>0.2707</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9589</v>
+        <v>-0.0649</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3664</v>
+        <v>0.3356</v>
       </c>
       <c r="V23" t="n">
         <v>0.3698</v>
@@ -2284,10 +2284,10 @@
         <v>-9.253299999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.811</v>
+        <v>-3.810800000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.4426</v>
+        <v>-5.4424</v>
       </c>
       <c r="G24" t="n">
         <v>-19.1681</v>
@@ -2299,13 +2299,13 @@
         <v>-13.7098</v>
       </c>
       <c r="J24" t="n">
-        <v>5.894499999999999</v>
+        <v>5.8945</v>
       </c>
       <c r="K24" t="n">
-        <v>3.683299999999999</v>
+        <v>3.683300000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>2.211399999999999</v>
+        <v>2.2114</v>
       </c>
       <c r="M24" t="n">
         <v>-25.0626</v>
@@ -2317,7 +2317,7 @@
         <v>-15.9214</v>
       </c>
       <c r="P24" t="n">
-        <v>2.175</v>
+        <v>2.174999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-18.488</v>
@@ -2326,19 +2326,19 @@
         <v>20.6631</v>
       </c>
       <c r="S24" t="n">
-        <v>6.8259</v>
+        <v>6.825799999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>2.896300000000001</v>
+        <v>2.8961</v>
       </c>
       <c r="U24" t="n">
-        <v>3.9294</v>
+        <v>3.9295</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9141000000000002</v>
+        <v>0.9140999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>5.886399999999999</v>
+        <v>5.8864</v>
       </c>
       <c r="X24" t="n">
         <v>-4.9725</v>
